--- a/cronograma_videojuego_v2.xlsx
+++ b/cronograma_videojuego_v2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsusTUF\OneDrive\Documentos\Descargas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsusTUF\OneDrive\Documentos\1.Universidad\7 Semestre\Diseño\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9D0CB1-018D-4192-9F3E-C3F3223CEAC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BCC4D9-CE89-4BDE-BB5A-BE0EFC4371C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,15 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="158">
   <si>
     <t>CRONOGRAMA DE PROYECTO – VIDEOJUEGO 3D EDUCATIVO</t>
   </si>
   <si>
     <t>Título del Proyecto:</t>
-  </si>
-  <si>
-    <t>VideoJuego 3D Educativo</t>
   </si>
   <si>
     <t>Gerente del Proyecto:</t>
@@ -484,6 +481,21 @@
   </si>
   <si>
     <t>Cierre</t>
+  </si>
+  <si>
+    <t>Recessed Minds</t>
+  </si>
+  <si>
+    <t>Se definio la estructura del proyecto del videojuego</t>
+  </si>
+  <si>
+    <t>Se identificaron los recursos y herramientas necesarias para el desarrollo del proyecto</t>
+  </si>
+  <si>
+    <t>Se realizo una estimacion general de costos del proyecto</t>
+  </si>
+  <si>
+    <t>Se identificaron posibles riesgos y estrategias de mitigacion</t>
   </si>
 </sst>
 </file>
@@ -806,7 +818,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -967,11 +979,6 @@
     <xf numFmtId="0" fontId="9" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="6" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -996,9 +1003,6 @@
     <xf numFmtId="14" fontId="6" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="6" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1015,6 +1019,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1248,98 +1257,98 @@
     <col min="4" max="4" width="28.44140625" customWidth="1"/>
     <col min="5" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="60" customWidth="1"/>
+    <col min="8" max="8" width="66.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="74"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="88"/>
     </row>
     <row r="2" spans="1:8" ht="16.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16.5" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="85">
+        <v>46074</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="89">
-        <v>46074</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="89">
+      <c r="E3" s="85">
         <v>46162</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.5" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="6" customHeight="1"/>
     <row r="6" spans="1:8" ht="30" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="78">
+      <c r="E7" s="75">
         <v>46074</v>
       </c>
-      <c r="F7" s="78">
+      <c r="F7" s="75">
         <v>46083</v>
       </c>
       <c r="G7" s="4">
@@ -1350,21 +1359,21 @@
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="77" t="s">
-        <v>132</v>
+      <c r="C8" s="74" t="s">
+        <v>131</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="76">
+        <v>21</v>
+      </c>
+      <c r="E8" s="73">
         <v>46074</v>
       </c>
-      <c r="F8" s="76">
+      <c r="F8" s="73">
         <v>46075</v>
       </c>
       <c r="G8" s="6">
@@ -1372,26 +1381,26 @@
         <v>1</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="C9" s="74" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="77" t="s">
-        <v>132</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="76">
+      <c r="E9" s="73">
         <v>46074</v>
       </c>
-      <c r="F9" s="79">
+      <c r="F9" s="76">
         <v>46077</v>
       </c>
       <c r="G9" s="6">
@@ -1399,26 +1408,26 @@
         <v>3</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="74" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="77" t="s">
-        <v>132</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="76">
+      <c r="E10" s="73">
         <v>46074</v>
       </c>
-      <c r="F10" s="76">
+      <c r="F10" s="73">
         <v>46081</v>
       </c>
       <c r="G10" s="6">
@@ -1426,26 +1435,26 @@
         <v>7</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="77" t="s">
-        <v>132</v>
+      <c r="C11" s="74" t="s">
+        <v>131</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="76">
+        <v>25</v>
+      </c>
+      <c r="E11" s="73">
         <v>46074</v>
       </c>
-      <c r="F11" s="79">
+      <c r="F11" s="76">
         <v>46081</v>
       </c>
       <c r="G11" s="6">
@@ -1453,26 +1462,26 @@
         <v>7</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="77" t="s">
-        <v>132</v>
+      <c r="C12" s="74" t="s">
+        <v>131</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="76">
+        <v>25</v>
+      </c>
+      <c r="E12" s="73">
         <v>46074</v>
       </c>
-      <c r="F12" s="76">
+      <c r="F12" s="73">
         <v>46081</v>
       </c>
       <c r="G12" s="6">
@@ -1480,26 +1489,26 @@
         <v>7</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="C13" s="74" t="s">
+        <v>131</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="77" t="s">
-        <v>132</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="76">
+      <c r="E13" s="73">
         <v>46082</v>
       </c>
-      <c r="F13" s="79">
+      <c r="F13" s="76">
         <v>46083</v>
       </c>
       <c r="G13" s="6">
@@ -1507,26 +1516,26 @@
         <v>1</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1">
       <c r="A14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="C14" s="74" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="77" t="s">
-        <v>132</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="76">
+      <c r="E14" s="73">
         <v>46082</v>
       </c>
-      <c r="F14" s="76">
+      <c r="F14" s="73">
         <v>46083</v>
       </c>
       <c r="G14" s="6">
@@ -1534,22 +1543,22 @@
         <v>1</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>46</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>47</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
-      <c r="E15" s="80">
+      <c r="E15" s="77">
         <v>46084</v>
       </c>
-      <c r="F15" s="80">
+      <c r="F15" s="77">
         <v>46091</v>
       </c>
       <c r="G15" s="10">
@@ -1560,117 +1569,125 @@
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="77" t="s">
-        <v>132</v>
+      <c r="C16" s="74" t="s">
+        <v>131</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="76">
+        <v>25</v>
+      </c>
+      <c r="E16" s="73">
         <v>46084</v>
       </c>
-      <c r="F16" s="76">
+      <c r="F16" s="73">
         <v>46085</v>
       </c>
       <c r="G16" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H16" s="7"/>
+      <c r="H16" s="7" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="77" t="s">
-        <v>132</v>
+      <c r="C17" s="74" t="s">
+        <v>131</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="79">
+        <v>29</v>
+      </c>
+      <c r="E17" s="76">
         <v>46086</v>
       </c>
-      <c r="F17" s="79">
+      <c r="F17" s="76">
         <v>46087</v>
       </c>
       <c r="G17" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H17" s="9"/>
+      <c r="H17" s="7" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="77" t="s">
-        <v>132</v>
+      <c r="C18" s="74" t="s">
+        <v>131</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="76">
+        <v>29</v>
+      </c>
+      <c r="E18" s="73">
         <v>46088</v>
       </c>
-      <c r="F18" s="76">
+      <c r="F18" s="73">
         <v>46089</v>
       </c>
       <c r="G18" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H18" s="7"/>
+      <c r="H18" s="7" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1">
       <c r="A19" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="77" t="s">
-        <v>132</v>
+      <c r="C19" s="74" t="s">
+        <v>131</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" s="79">
+        <v>39</v>
+      </c>
+      <c r="E19" s="76">
         <v>46090</v>
       </c>
-      <c r="F19" s="79">
+      <c r="F19" s="76">
         <v>46091</v>
       </c>
       <c r="G19" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H19" s="9"/>
+      <c r="H19" s="7" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="14" t="s">
         <v>57</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>58</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
-      <c r="E20" s="75">
+      <c r="E20" s="72">
         <v>46092</v>
       </c>
-      <c r="F20" s="75">
+      <c r="F20" s="72">
         <v>46108</v>
       </c>
       <c r="G20" s="13">
@@ -1681,21 +1698,21 @@
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="81" t="s">
-        <v>21</v>
+      <c r="C21" s="78" t="s">
+        <v>20</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" s="79">
+        <v>43</v>
+      </c>
+      <c r="E21" s="76">
         <v>46092</v>
       </c>
-      <c r="F21" s="79">
+      <c r="F21" s="76">
         <v>46106</v>
       </c>
       <c r="G21" s="6">
@@ -1706,21 +1723,21 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1">
       <c r="A22" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="81" t="s">
-        <v>21</v>
+      <c r="C22" s="78" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="79">
+        <v>43</v>
+      </c>
+      <c r="E22" s="76">
         <v>46092</v>
       </c>
-      <c r="F22" s="79">
+      <c r="F22" s="76">
         <v>46106</v>
       </c>
       <c r="G22" s="6">
@@ -1731,21 +1748,21 @@
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1">
       <c r="A23" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="81" t="s">
-        <v>21</v>
+      <c r="C23" s="78" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="79">
+        <v>25</v>
+      </c>
+      <c r="E23" s="76">
         <v>46092</v>
       </c>
-      <c r="F23" s="79">
+      <c r="F23" s="76">
         <v>46106</v>
       </c>
       <c r="G23" s="6">
@@ -1756,21 +1773,21 @@
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1">
       <c r="A24" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="81" t="s">
-        <v>21</v>
+      <c r="C24" s="78" t="s">
+        <v>20</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" s="79">
+        <v>39</v>
+      </c>
+      <c r="E24" s="76">
         <v>46092</v>
       </c>
-      <c r="F24" s="79">
+      <c r="F24" s="76">
         <v>46106</v>
       </c>
       <c r="G24" s="6">
@@ -1781,21 +1798,21 @@
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1">
       <c r="A25" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" s="81" t="s">
-        <v>21</v>
+      <c r="C25" s="78" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="79">
+        <v>25</v>
+      </c>
+      <c r="E25" s="76">
         <v>46092</v>
       </c>
-      <c r="F25" s="79">
+      <c r="F25" s="76">
         <v>46108</v>
       </c>
       <c r="G25" s="6">
@@ -1806,21 +1823,21 @@
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" s="81" t="s">
-        <v>21</v>
+      <c r="C26" s="78" t="s">
+        <v>20</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" s="79">
+        <v>43</v>
+      </c>
+      <c r="E26" s="76">
         <v>46092</v>
       </c>
-      <c r="F26" s="79">
+      <c r="F26" s="76">
         <v>46106</v>
       </c>
       <c r="G26" s="6">
@@ -1831,21 +1848,21 @@
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
       <c r="A27" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="81" t="s">
-        <v>21</v>
+      <c r="C27" s="78" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27" s="79">
+        <v>29</v>
+      </c>
+      <c r="E27" s="76">
         <v>46092</v>
       </c>
-      <c r="F27" s="79">
+      <c r="F27" s="76">
         <v>46108</v>
       </c>
       <c r="G27" s="6">
@@ -1856,21 +1873,21 @@
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1">
       <c r="A28" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="81" t="s">
-        <v>21</v>
+      <c r="C28" s="78" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="79">
+        <v>43</v>
+      </c>
+      <c r="E28" s="76">
         <v>46092</v>
       </c>
-      <c r="F28" s="79">
+      <c r="F28" s="76">
         <v>46108</v>
       </c>
       <c r="G28" s="6">
@@ -1881,21 +1898,21 @@
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1">
       <c r="A29" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" s="81" t="s">
-        <v>21</v>
+      <c r="C29" s="78" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E29" s="79">
+        <v>25</v>
+      </c>
+      <c r="E29" s="76">
         <v>46092</v>
       </c>
-      <c r="F29" s="79">
+      <c r="F29" s="76">
         <v>46108</v>
       </c>
       <c r="G29" s="6">
@@ -1906,21 +1923,21 @@
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1">
       <c r="A30" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="81" t="s">
-        <v>21</v>
+      <c r="C30" s="78" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="79">
+        <v>29</v>
+      </c>
+      <c r="E30" s="76">
         <v>46092</v>
       </c>
-      <c r="F30" s="79">
+      <c r="F30" s="76">
         <v>46108</v>
       </c>
       <c r="G30" s="6">
@@ -1931,20 +1948,20 @@
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1">
       <c r="A31" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" s="16" t="s">
         <v>79</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>80</v>
       </c>
       <c r="C31" s="15"/>
       <c r="D31" s="15"/>
-      <c r="E31" s="82">
+      <c r="E31" s="79">
         <v>46109</v>
       </c>
-      <c r="F31" s="82">
+      <c r="F31" s="79">
         <v>46142</v>
       </c>
-      <c r="G31" s="83">
+      <c r="G31" s="15">
         <f>F31-E31</f>
         <v>33</v>
       </c>
@@ -1952,21 +1969,21 @@
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1">
       <c r="A32" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="C32" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="76">
+        <v>29</v>
+      </c>
+      <c r="E32" s="73">
         <v>46109</v>
       </c>
-      <c r="F32" s="76">
+      <c r="F32" s="73">
         <v>46110</v>
       </c>
       <c r="G32" s="6">
@@ -1977,21 +1994,21 @@
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1">
       <c r="A33" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>84</v>
-      </c>
       <c r="C33" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" s="79">
+        <v>43</v>
+      </c>
+      <c r="E33" s="76">
         <v>46111</v>
       </c>
-      <c r="F33" s="79">
+      <c r="F33" s="76">
         <v>46122</v>
       </c>
       <c r="G33" s="6">
@@ -2002,21 +2019,21 @@
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1">
       <c r="A34" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>86</v>
-      </c>
       <c r="C34" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" s="76">
+        <v>25</v>
+      </c>
+      <c r="E34" s="73">
         <v>46123</v>
       </c>
-      <c r="F34" s="76">
+      <c r="F34" s="73">
         <v>46127</v>
       </c>
       <c r="G34" s="6">
@@ -2027,21 +2044,21 @@
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1">
       <c r="A35" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>88</v>
-      </c>
       <c r="C35" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35" s="79">
+        <v>25</v>
+      </c>
+      <c r="E35" s="76">
         <v>46128</v>
       </c>
-      <c r="F35" s="79">
+      <c r="F35" s="76">
         <v>46131</v>
       </c>
       <c r="G35" s="6">
@@ -2052,21 +2069,21 @@
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1">
       <c r="A36" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="C36" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E36" s="76">
+        <v>39</v>
+      </c>
+      <c r="E36" s="73">
         <v>46132</v>
       </c>
-      <c r="F36" s="76">
+      <c r="F36" s="73">
         <v>46136</v>
       </c>
       <c r="G36" s="6">
@@ -2077,21 +2094,21 @@
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1">
       <c r="A37" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B37" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="C37" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E37" s="79">
+        <v>43</v>
+      </c>
+      <c r="E37" s="76">
         <v>46137</v>
       </c>
-      <c r="F37" s="79">
+      <c r="F37" s="76">
         <v>46142</v>
       </c>
       <c r="G37" s="6">
@@ -2102,17 +2119,17 @@
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1">
       <c r="A38" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="18" t="s">
         <v>93</v>
-      </c>
-      <c r="B38" s="18" t="s">
-        <v>94</v>
       </c>
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
-      <c r="E38" s="84">
+      <c r="E38" s="80">
         <v>46143</v>
       </c>
-      <c r="F38" s="85">
+      <c r="F38" s="81">
         <v>46152</v>
       </c>
       <c r="G38" s="17">
@@ -2123,21 +2140,21 @@
     </row>
     <row r="39" spans="1:8" ht="15.75" customHeight="1">
       <c r="A39" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B39" s="9" t="s">
-        <v>96</v>
-      </c>
       <c r="C39" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E39" s="79">
+        <v>29</v>
+      </c>
+      <c r="E39" s="76">
         <v>46143</v>
       </c>
-      <c r="F39" s="79">
+      <c r="F39" s="76">
         <v>46145</v>
       </c>
       <c r="G39" s="8">
@@ -2148,21 +2165,21 @@
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1">
       <c r="A40" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>98</v>
-      </c>
       <c r="C40" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="76">
+        <v>43</v>
+      </c>
+      <c r="E40" s="73">
         <v>46146</v>
       </c>
-      <c r="F40" s="76">
+      <c r="F40" s="73">
         <v>46147</v>
       </c>
       <c r="G40" s="8">
@@ -2173,21 +2190,21 @@
     </row>
     <row r="41" spans="1:8" ht="15.75" customHeight="1">
       <c r="A41" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B41" s="9" t="s">
-        <v>100</v>
-      </c>
       <c r="C41" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E41" s="79">
+        <v>25</v>
+      </c>
+      <c r="E41" s="76">
         <v>46148</v>
       </c>
-      <c r="F41" s="79">
+      <c r="F41" s="76">
         <v>46149</v>
       </c>
       <c r="G41" s="8">
@@ -2198,21 +2215,21 @@
     </row>
     <row r="42" spans="1:8" ht="15.75" customHeight="1">
       <c r="A42" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B42" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>102</v>
-      </c>
       <c r="C42" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E42" s="76">
+        <v>39</v>
+      </c>
+      <c r="E42" s="73">
         <v>46150</v>
       </c>
-      <c r="F42" s="76">
+      <c r="F42" s="73">
         <v>46151</v>
       </c>
       <c r="G42" s="8">
@@ -2223,21 +2240,21 @@
     </row>
     <row r="43" spans="1:8" ht="15.75" customHeight="1">
       <c r="A43" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B43" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B43" s="9" t="s">
-        <v>104</v>
-      </c>
       <c r="C43" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E43" s="79">
+        <v>25</v>
+      </c>
+      <c r="E43" s="76">
         <v>46143</v>
       </c>
-      <c r="F43" s="79">
+      <c r="F43" s="76">
         <v>46152</v>
       </c>
       <c r="G43" s="8">
@@ -2248,17 +2265,17 @@
     </row>
     <row r="44" spans="1:8" ht="15.75" customHeight="1">
       <c r="A44" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" s="20" t="s">
         <v>105</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>106</v>
       </c>
       <c r="C44" s="19"/>
       <c r="D44" s="19"/>
-      <c r="E44" s="86">
+      <c r="E44" s="82">
         <v>46153</v>
       </c>
-      <c r="F44" s="86">
+      <c r="F44" s="82">
         <v>46157</v>
       </c>
       <c r="G44" s="19">
@@ -2269,21 +2286,21 @@
     </row>
     <row r="45" spans="1:8" ht="15.75" customHeight="1">
       <c r="A45" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B45" s="9" t="s">
-        <v>108</v>
-      </c>
       <c r="C45" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E45" s="79">
+        <v>29</v>
+      </c>
+      <c r="E45" s="76">
         <v>46153</v>
       </c>
-      <c r="F45" s="79">
+      <c r="F45" s="76">
         <v>46154</v>
       </c>
       <c r="G45" s="8">
@@ -2294,21 +2311,21 @@
     </row>
     <row r="46" spans="1:8" ht="15.75" customHeight="1">
       <c r="A46" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>110</v>
-      </c>
       <c r="C46" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E46" s="76">
+        <v>29</v>
+      </c>
+      <c r="E46" s="73">
         <v>46154</v>
       </c>
-      <c r="F46" s="76">
+      <c r="F46" s="73">
         <v>46155</v>
       </c>
       <c r="G46" s="8">
@@ -2319,21 +2336,21 @@
     </row>
     <row r="47" spans="1:8" ht="15.75" customHeight="1">
       <c r="A47" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B47" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B47" s="9" t="s">
-        <v>112</v>
-      </c>
       <c r="C47" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E47" s="79">
+        <v>25</v>
+      </c>
+      <c r="E47" s="76">
         <v>46155</v>
       </c>
-      <c r="F47" s="79">
+      <c r="F47" s="76">
         <v>46156</v>
       </c>
       <c r="G47" s="8">
@@ -2344,21 +2361,21 @@
     </row>
     <row r="48" spans="1:8" ht="15.75" customHeight="1">
       <c r="A48" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B48" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>114</v>
-      </c>
       <c r="C48" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E48" s="76">
+        <v>21</v>
+      </c>
+      <c r="E48" s="73">
         <v>46156</v>
       </c>
-      <c r="F48" s="76">
+      <c r="F48" s="73">
         <v>46157</v>
       </c>
       <c r="G48" s="8">
@@ -2369,17 +2386,17 @@
     </row>
     <row r="49" spans="1:9" ht="15.75" customHeight="1">
       <c r="A49" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B49" s="22" t="s">
         <v>115</v>
-      </c>
-      <c r="B49" s="22" t="s">
-        <v>116</v>
       </c>
       <c r="C49" s="21"/>
       <c r="D49" s="21"/>
-      <c r="E49" s="87">
+      <c r="E49" s="83">
         <v>46158</v>
       </c>
-      <c r="F49" s="87">
+      <c r="F49" s="83">
         <v>46161</v>
       </c>
       <c r="G49" s="21">
@@ -2390,21 +2407,21 @@
     </row>
     <row r="50" spans="1:9" ht="15.75" customHeight="1">
       <c r="A50" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>118</v>
-      </c>
       <c r="C50" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E50" s="76">
+        <v>25</v>
+      </c>
+      <c r="E50" s="73">
         <v>46158</v>
       </c>
-      <c r="F50" s="76">
+      <c r="F50" s="73">
         <v>46159</v>
       </c>
       <c r="G50" s="6">
@@ -2415,21 +2432,21 @@
     </row>
     <row r="51" spans="1:9" ht="15.75" customHeight="1">
       <c r="A51" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B51" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B51" s="9" t="s">
-        <v>120</v>
-      </c>
       <c r="C51" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E51" s="79">
+        <v>39</v>
+      </c>
+      <c r="E51" s="76">
         <v>46159</v>
       </c>
-      <c r="F51" s="79">
+      <c r="F51" s="76">
         <v>46160</v>
       </c>
       <c r="G51" s="6">
@@ -2440,21 +2457,21 @@
     </row>
     <row r="52" spans="1:9" ht="15.75" customHeight="1">
       <c r="A52" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B52" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B52" s="7" t="s">
-        <v>122</v>
-      </c>
       <c r="C52" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E52" s="76">
+        <v>25</v>
+      </c>
+      <c r="E52" s="73">
         <v>46160</v>
       </c>
-      <c r="F52" s="76">
+      <c r="F52" s="73">
         <v>46161</v>
       </c>
       <c r="G52" s="6">
@@ -2465,21 +2482,21 @@
     </row>
     <row r="53" spans="1:9" ht="15.75" customHeight="1">
       <c r="A53" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="B53" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B53" s="9" t="s">
-        <v>124</v>
-      </c>
       <c r="C53" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E53" s="79">
+        <v>21</v>
+      </c>
+      <c r="E53" s="76">
         <v>46160</v>
       </c>
-      <c r="F53" s="79">
+      <c r="F53" s="76">
         <v>46161</v>
       </c>
       <c r="G53" s="6">
@@ -2490,21 +2507,21 @@
     </row>
     <row r="54" spans="1:9" ht="15.75" customHeight="1">
       <c r="A54" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B54" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B54" s="7" t="s">
-        <v>126</v>
-      </c>
       <c r="C54" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E54" s="76">
+        <v>21</v>
+      </c>
+      <c r="E54" s="73">
         <v>46160</v>
       </c>
-      <c r="F54" s="76">
+      <c r="F54" s="73">
         <v>46161</v>
       </c>
       <c r="G54" s="6">
@@ -2515,17 +2532,17 @@
     </row>
     <row r="55" spans="1:9" ht="15.75" customHeight="1">
       <c r="A55" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="B55" s="24" t="s">
         <v>127</v>
-      </c>
-      <c r="B55" s="24" t="s">
-        <v>128</v>
       </c>
       <c r="C55" s="23"/>
       <c r="D55" s="23"/>
-      <c r="E55" s="88">
+      <c r="E55" s="84">
         <v>46161</v>
       </c>
-      <c r="F55" s="88">
+      <c r="F55" s="84">
         <v>46162</v>
       </c>
       <c r="G55" s="23">
@@ -2536,21 +2553,21 @@
     </row>
     <row r="56" spans="1:9" ht="15.75" customHeight="1">
       <c r="A56" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B56" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B56" s="7" t="s">
-        <v>130</v>
-      </c>
       <c r="C56" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E56" s="76">
+        <v>21</v>
+      </c>
+      <c r="E56" s="73">
         <v>46161</v>
       </c>
-      <c r="F56" s="76">
+      <c r="F56" s="73">
         <v>46162</v>
       </c>
       <c r="G56" s="6">
@@ -2563,23 +2580,23 @@
     <row r="58" spans="1:9" ht="15.75" customHeight="1"/>
     <row r="59" spans="1:9" ht="15.75" customHeight="1">
       <c r="A59" s="25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B59" s="26"/>
       <c r="C59" s="27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D59" s="28"/>
       <c r="E59" s="27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F59" s="29"/>
       <c r="G59" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H59" s="30"/>
       <c r="I59" s="27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15.75" customHeight="1"/>
@@ -3550,82 +3567,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" ht="25.5" customHeight="1">
-      <c r="A1" s="72" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="73"/>
-      <c r="AD1" s="73"/>
-      <c r="AE1" s="73"/>
-      <c r="AF1" s="73"/>
-      <c r="AG1" s="73"/>
-      <c r="AH1" s="73"/>
-      <c r="AI1" s="73"/>
-      <c r="AJ1" s="73"/>
-      <c r="AK1" s="73"/>
-      <c r="AL1" s="73"/>
-      <c r="AM1" s="73"/>
-      <c r="AN1" s="73"/>
-      <c r="AO1" s="73"/>
-      <c r="AP1" s="73"/>
-      <c r="AQ1" s="73"/>
-      <c r="AR1" s="73"/>
-      <c r="AS1" s="73"/>
-      <c r="AT1" s="73"/>
-      <c r="AU1" s="73"/>
-      <c r="AV1" s="73"/>
-      <c r="AW1" s="73"/>
-      <c r="AX1" s="73"/>
-      <c r="AY1" s="73"/>
-      <c r="AZ1" s="73"/>
-      <c r="BA1" s="73"/>
-      <c r="BB1" s="73"/>
-      <c r="BC1" s="73"/>
-      <c r="BD1" s="73"/>
-      <c r="BE1" s="73"/>
-      <c r="BF1" s="73"/>
-      <c r="BG1" s="74"/>
+      <c r="A1" s="86" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="87"/>
+      <c r="L1" s="87"/>
+      <c r="M1" s="87"/>
+      <c r="N1" s="87"/>
+      <c r="O1" s="87"/>
+      <c r="P1" s="87"/>
+      <c r="Q1" s="87"/>
+      <c r="R1" s="87"/>
+      <c r="S1" s="87"/>
+      <c r="T1" s="87"/>
+      <c r="U1" s="87"/>
+      <c r="V1" s="87"/>
+      <c r="W1" s="87"/>
+      <c r="X1" s="87"/>
+      <c r="Y1" s="87"/>
+      <c r="Z1" s="87"/>
+      <c r="AA1" s="87"/>
+      <c r="AB1" s="87"/>
+      <c r="AC1" s="87"/>
+      <c r="AD1" s="87"/>
+      <c r="AE1" s="87"/>
+      <c r="AF1" s="87"/>
+      <c r="AG1" s="87"/>
+      <c r="AH1" s="87"/>
+      <c r="AI1" s="87"/>
+      <c r="AJ1" s="87"/>
+      <c r="AK1" s="87"/>
+      <c r="AL1" s="87"/>
+      <c r="AM1" s="87"/>
+      <c r="AN1" s="87"/>
+      <c r="AO1" s="87"/>
+      <c r="AP1" s="87"/>
+      <c r="AQ1" s="87"/>
+      <c r="AR1" s="87"/>
+      <c r="AS1" s="87"/>
+      <c r="AT1" s="87"/>
+      <c r="AU1" s="87"/>
+      <c r="AV1" s="87"/>
+      <c r="AW1" s="87"/>
+      <c r="AX1" s="87"/>
+      <c r="AY1" s="87"/>
+      <c r="AZ1" s="87"/>
+      <c r="BA1" s="87"/>
+      <c r="BB1" s="87"/>
+      <c r="BC1" s="87"/>
+      <c r="BD1" s="87"/>
+      <c r="BE1" s="87"/>
+      <c r="BF1" s="87"/>
+      <c r="BG1" s="88"/>
     </row>
     <row r="2" spans="1:59" ht="27.75" customHeight="1">
       <c r="A2" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="32" t="s">
         <v>135</v>
-      </c>
-      <c r="B2" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="32" t="s">
-        <v>136</v>
       </c>
       <c r="D2" s="32"/>
       <c r="E2" s="32"/>
       <c r="F2" s="32" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
@@ -3634,7 +3651,7 @@
       <c r="K2" s="32"/>
       <c r="L2" s="32"/>
       <c r="M2" s="32" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N2" s="32"/>
       <c r="O2" s="32"/>
@@ -3643,7 +3660,7 @@
       <c r="R2" s="32"/>
       <c r="S2" s="32"/>
       <c r="T2" s="32" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="U2" s="32"/>
       <c r="V2" s="32"/>
@@ -3652,7 +3669,7 @@
       <c r="Y2" s="32"/>
       <c r="Z2" s="32"/>
       <c r="AA2" s="32" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AB2" s="32"/>
       <c r="AC2" s="32"/>
@@ -3661,7 +3678,7 @@
       <c r="AF2" s="32"/>
       <c r="AG2" s="32"/>
       <c r="AH2" s="32" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AI2" s="32"/>
       <c r="AJ2" s="32"/>
@@ -3670,7 +3687,7 @@
       <c r="AM2" s="32"/>
       <c r="AN2" s="32"/>
       <c r="AO2" s="32" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AP2" s="32"/>
       <c r="AQ2" s="32"/>
@@ -3679,7 +3696,7 @@
       <c r="AT2" s="32"/>
       <c r="AU2" s="32"/>
       <c r="AV2" s="32" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AW2" s="32"/>
       <c r="AX2" s="32"/>
@@ -3688,7 +3705,7 @@
       <c r="BA2" s="32"/>
       <c r="BB2" s="32"/>
       <c r="BC2" s="32" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="BD2" s="32"/>
       <c r="BE2" s="32"/>
@@ -3697,10 +3714,10 @@
     </row>
     <row r="3" spans="1:59" ht="13.5" customHeight="1">
       <c r="A3" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="34" t="s">
         <v>17</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>18</v>
       </c>
       <c r="C3" s="35"/>
       <c r="D3" s="35"/>
@@ -3762,10 +3779,10 @@
     </row>
     <row r="4" spans="1:59" ht="13.5" customHeight="1">
       <c r="A4" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="38" t="s">
         <v>19</v>
-      </c>
-      <c r="B4" s="38" t="s">
-        <v>20</v>
       </c>
       <c r="C4" s="35"/>
       <c r="D4" s="35"/>
@@ -3827,10 +3844,10 @@
     </row>
     <row r="5" spans="1:59" ht="13.5" customHeight="1">
       <c r="A5" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="41" t="s">
         <v>24</v>
-      </c>
-      <c r="B5" s="41" t="s">
-        <v>25</v>
       </c>
       <c r="C5" s="35"/>
       <c r="D5" s="35"/>
@@ -3892,10 +3909,10 @@
     </row>
     <row r="6" spans="1:59" ht="13.5" customHeight="1">
       <c r="A6" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="38" t="s">
         <v>28</v>
-      </c>
-      <c r="B6" s="38" t="s">
-        <v>29</v>
       </c>
       <c r="C6" s="35"/>
       <c r="D6" s="35"/>
@@ -3957,10 +3974,10 @@
     </row>
     <row r="7" spans="1:59" ht="13.5" customHeight="1">
       <c r="A7" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="41" t="s">
         <v>32</v>
-      </c>
-      <c r="B7" s="41" t="s">
-        <v>33</v>
       </c>
       <c r="C7" s="35"/>
       <c r="D7" s="35"/>
@@ -4022,10 +4039,10 @@
     </row>
     <row r="8" spans="1:59" ht="13.5" customHeight="1">
       <c r="A8" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="38" t="s">
         <v>35</v>
-      </c>
-      <c r="B8" s="38" t="s">
-        <v>36</v>
       </c>
       <c r="C8" s="35"/>
       <c r="D8" s="35"/>
@@ -4087,10 +4104,10 @@
     </row>
     <row r="9" spans="1:59" ht="13.5" customHeight="1">
       <c r="A9" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="41" t="s">
         <v>38</v>
-      </c>
-      <c r="B9" s="41" t="s">
-        <v>39</v>
       </c>
       <c r="C9" s="35"/>
       <c r="D9" s="35"/>
@@ -4152,10 +4169,10 @@
     </row>
     <row r="10" spans="1:59" ht="13.5" customHeight="1">
       <c r="A10" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="38" t="s">
         <v>42</v>
-      </c>
-      <c r="B10" s="38" t="s">
-        <v>43</v>
       </c>
       <c r="C10" s="35"/>
       <c r="D10" s="35"/>
@@ -4217,10 +4234,10 @@
     </row>
     <row r="11" spans="1:59" ht="13.5" customHeight="1">
       <c r="A11" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="43" t="s">
         <v>46</v>
-      </c>
-      <c r="B11" s="43" t="s">
-        <v>47</v>
       </c>
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
@@ -4282,10 +4299,10 @@
     </row>
     <row r="12" spans="1:59" ht="13.5" customHeight="1">
       <c r="A12" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="38" t="s">
         <v>48</v>
-      </c>
-      <c r="B12" s="38" t="s">
-        <v>49</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
@@ -4347,10 +4364,10 @@
     </row>
     <row r="13" spans="1:59" ht="13.5" customHeight="1">
       <c r="A13" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="41" t="s">
         <v>51</v>
-      </c>
-      <c r="B13" s="41" t="s">
-        <v>52</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -4412,10 +4429,10 @@
     </row>
     <row r="14" spans="1:59" ht="13.5" customHeight="1">
       <c r="A14" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="38" t="s">
         <v>53</v>
-      </c>
-      <c r="B14" s="38" t="s">
-        <v>54</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -4477,10 +4494,10 @@
     </row>
     <row r="15" spans="1:59" ht="13.5" customHeight="1">
       <c r="A15" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="41" t="s">
         <v>55</v>
-      </c>
-      <c r="B15" s="41" t="s">
-        <v>56</v>
       </c>
       <c r="C15" s="39"/>
       <c r="D15" s="39"/>
@@ -4542,10 +4559,10 @@
     </row>
     <row r="16" spans="1:59" ht="13.5" customHeight="1">
       <c r="A16" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="46" t="s">
         <v>57</v>
-      </c>
-      <c r="B16" s="46" t="s">
-        <v>58</v>
       </c>
       <c r="C16" s="36"/>
       <c r="D16" s="36"/>
@@ -4607,10 +4624,10 @@
     </row>
     <row r="17" spans="1:59" ht="13.5" customHeight="1">
       <c r="A17" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="41" t="s">
         <v>59</v>
-      </c>
-      <c r="B17" s="41" t="s">
-        <v>60</v>
       </c>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
@@ -4672,10 +4689,10 @@
     </row>
     <row r="18" spans="1:59" ht="13.5" customHeight="1">
       <c r="A18" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="38" t="s">
         <v>61</v>
-      </c>
-      <c r="B18" s="38" t="s">
-        <v>62</v>
       </c>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -4737,10 +4754,10 @@
     </row>
     <row r="19" spans="1:59" ht="13.5" customHeight="1">
       <c r="A19" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="41" t="s">
         <v>63</v>
-      </c>
-      <c r="B19" s="41" t="s">
-        <v>64</v>
       </c>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
@@ -4802,10 +4819,10 @@
     </row>
     <row r="20" spans="1:59" ht="13.5" customHeight="1">
       <c r="A20" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="38" t="s">
         <v>65</v>
-      </c>
-      <c r="B20" s="38" t="s">
-        <v>66</v>
       </c>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -4867,10 +4884,10 @@
     </row>
     <row r="21" spans="1:59" ht="13.5" customHeight="1">
       <c r="A21" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="41" t="s">
         <v>67</v>
-      </c>
-      <c r="B21" s="41" t="s">
-        <v>68</v>
       </c>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -4932,10 +4949,10 @@
     </row>
     <row r="22" spans="1:59" ht="13.5" customHeight="1">
       <c r="A22" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="38" t="s">
         <v>69</v>
-      </c>
-      <c r="B22" s="38" t="s">
-        <v>70</v>
       </c>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -4997,10 +5014,10 @@
     </row>
     <row r="23" spans="1:59" ht="13.5" customHeight="1">
       <c r="A23" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="41" t="s">
         <v>71</v>
-      </c>
-      <c r="B23" s="41" t="s">
-        <v>72</v>
       </c>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -5062,10 +5079,10 @@
     </row>
     <row r="24" spans="1:59" ht="13.5" customHeight="1">
       <c r="A24" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="38" t="s">
         <v>73</v>
-      </c>
-      <c r="B24" s="38" t="s">
-        <v>74</v>
       </c>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -5127,10 +5144,10 @@
     </row>
     <row r="25" spans="1:59" ht="13.5" customHeight="1">
       <c r="A25" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="41" t="s">
         <v>75</v>
-      </c>
-      <c r="B25" s="41" t="s">
-        <v>76</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="39"/>
@@ -5192,10 +5209,10 @@
     </row>
     <row r="26" spans="1:59" ht="13.5" customHeight="1">
       <c r="A26" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" s="38" t="s">
         <v>77</v>
-      </c>
-      <c r="B26" s="38" t="s">
-        <v>78</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -5257,10 +5274,10 @@
     </row>
     <row r="27" spans="1:59" ht="13.5" customHeight="1">
       <c r="A27" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="49" t="s">
         <v>79</v>
-      </c>
-      <c r="B27" s="49" t="s">
-        <v>80</v>
       </c>
       <c r="C27" s="36"/>
       <c r="D27" s="36"/>
@@ -5322,10 +5339,10 @@
     </row>
     <row r="28" spans="1:59" ht="13.5" customHeight="1">
       <c r="A28" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" s="38" t="s">
         <v>81</v>
-      </c>
-      <c r="B28" s="38" t="s">
-        <v>82</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -5387,10 +5404,10 @@
     </row>
     <row r="29" spans="1:59" ht="13.5" customHeight="1">
       <c r="A29" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="41" t="s">
         <v>83</v>
-      </c>
-      <c r="B29" s="41" t="s">
-        <v>84</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
@@ -5452,10 +5469,10 @@
     </row>
     <row r="30" spans="1:59" ht="13.5" customHeight="1">
       <c r="A30" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" s="38" t="s">
         <v>85</v>
-      </c>
-      <c r="B30" s="38" t="s">
-        <v>86</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -5517,10 +5534,10 @@
     </row>
     <row r="31" spans="1:59" ht="13.5" customHeight="1">
       <c r="A31" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="41" t="s">
         <v>87</v>
-      </c>
-      <c r="B31" s="41" t="s">
-        <v>88</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
@@ -5582,10 +5599,10 @@
     </row>
     <row r="32" spans="1:59" ht="13.5" customHeight="1">
       <c r="A32" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="38" t="s">
         <v>89</v>
-      </c>
-      <c r="B32" s="38" t="s">
-        <v>90</v>
       </c>
       <c r="C32" s="39"/>
       <c r="D32" s="39"/>
@@ -5647,10 +5664,10 @@
     </row>
     <row r="33" spans="1:59" ht="13.5" customHeight="1">
       <c r="A33" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="41" t="s">
         <v>91</v>
-      </c>
-      <c r="B33" s="41" t="s">
-        <v>92</v>
       </c>
       <c r="C33" s="39"/>
       <c r="D33" s="39"/>
@@ -5712,10 +5729,10 @@
     </row>
     <row r="34" spans="1:59" ht="13.5" customHeight="1">
       <c r="A34" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="52" t="s">
         <v>93</v>
-      </c>
-      <c r="B34" s="52" t="s">
-        <v>94</v>
       </c>
       <c r="C34" s="36"/>
       <c r="D34" s="36"/>
@@ -5777,10 +5794,10 @@
     </row>
     <row r="35" spans="1:59" ht="13.5" customHeight="1">
       <c r="A35" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="41" t="s">
         <v>95</v>
-      </c>
-      <c r="B35" s="41" t="s">
-        <v>96</v>
       </c>
       <c r="C35" s="39"/>
       <c r="D35" s="39"/>
@@ -5842,10 +5859,10 @@
     </row>
     <row r="36" spans="1:59" ht="13.5" customHeight="1">
       <c r="A36" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="38" t="s">
         <v>97</v>
-      </c>
-      <c r="B36" s="38" t="s">
-        <v>98</v>
       </c>
       <c r="C36" s="39"/>
       <c r="D36" s="39"/>
@@ -5907,10 +5924,10 @@
     </row>
     <row r="37" spans="1:59" ht="13.5" customHeight="1">
       <c r="A37" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="41" t="s">
         <v>99</v>
-      </c>
-      <c r="B37" s="41" t="s">
-        <v>100</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
@@ -5972,10 +5989,10 @@
     </row>
     <row r="38" spans="1:59" ht="13.5" customHeight="1">
       <c r="A38" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" s="38" t="s">
         <v>101</v>
-      </c>
-      <c r="B38" s="38" t="s">
-        <v>102</v>
       </c>
       <c r="C38" s="39"/>
       <c r="D38" s="39"/>
@@ -6037,10 +6054,10 @@
     </row>
     <row r="39" spans="1:59" ht="13.5" customHeight="1">
       <c r="A39" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="41" t="s">
         <v>103</v>
-      </c>
-      <c r="B39" s="41" t="s">
-        <v>104</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
@@ -6102,10 +6119,10 @@
     </row>
     <row r="40" spans="1:59" ht="13.5" customHeight="1">
       <c r="A40" s="54" t="s">
+        <v>104</v>
+      </c>
+      <c r="B40" s="55" t="s">
         <v>105</v>
-      </c>
-      <c r="B40" s="55" t="s">
-        <v>106</v>
       </c>
       <c r="C40" s="36"/>
       <c r="D40" s="36"/>
@@ -6167,10 +6184,10 @@
     </row>
     <row r="41" spans="1:59" ht="13.5" customHeight="1">
       <c r="A41" s="40" t="s">
+        <v>106</v>
+      </c>
+      <c r="B41" s="41" t="s">
         <v>107</v>
-      </c>
-      <c r="B41" s="41" t="s">
-        <v>108</v>
       </c>
       <c r="C41" s="39"/>
       <c r="D41" s="39"/>
@@ -6232,10 +6249,10 @@
     </row>
     <row r="42" spans="1:59" ht="13.5" customHeight="1">
       <c r="A42" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42" s="38" t="s">
         <v>109</v>
-      </c>
-      <c r="B42" s="38" t="s">
-        <v>110</v>
       </c>
       <c r="C42" s="39"/>
       <c r="D42" s="39"/>
@@ -6297,10 +6314,10 @@
     </row>
     <row r="43" spans="1:59" ht="13.5" customHeight="1">
       <c r="A43" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="B43" s="41" t="s">
         <v>111</v>
-      </c>
-      <c r="B43" s="41" t="s">
-        <v>112</v>
       </c>
       <c r="C43" s="39"/>
       <c r="D43" s="39"/>
@@ -6362,10 +6379,10 @@
     </row>
     <row r="44" spans="1:59" ht="13.5" customHeight="1">
       <c r="A44" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="B44" s="38" t="s">
         <v>113</v>
-      </c>
-      <c r="B44" s="38" t="s">
-        <v>114</v>
       </c>
       <c r="C44" s="39"/>
       <c r="D44" s="39"/>
@@ -6427,10 +6444,10 @@
     </row>
     <row r="45" spans="1:59" ht="13.5" customHeight="1">
       <c r="A45" s="57" t="s">
+        <v>114</v>
+      </c>
+      <c r="B45" s="58" t="s">
         <v>115</v>
-      </c>
-      <c r="B45" s="58" t="s">
-        <v>116</v>
       </c>
       <c r="C45" s="36"/>
       <c r="D45" s="36"/>
@@ -6492,10 +6509,10 @@
     </row>
     <row r="46" spans="1:59" ht="13.5" customHeight="1">
       <c r="A46" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="B46" s="38" t="s">
         <v>117</v>
-      </c>
-      <c r="B46" s="38" t="s">
-        <v>118</v>
       </c>
       <c r="C46" s="39"/>
       <c r="D46" s="39"/>
@@ -6557,10 +6574,10 @@
     </row>
     <row r="47" spans="1:59" ht="13.5" customHeight="1">
       <c r="A47" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" s="41" t="s">
         <v>119</v>
-      </c>
-      <c r="B47" s="41" t="s">
-        <v>120</v>
       </c>
       <c r="C47" s="39"/>
       <c r="D47" s="39"/>
@@ -6622,10 +6639,10 @@
     </row>
     <row r="48" spans="1:59" ht="13.5" customHeight="1">
       <c r="A48" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="B48" s="38" t="s">
         <v>121</v>
-      </c>
-      <c r="B48" s="38" t="s">
-        <v>122</v>
       </c>
       <c r="C48" s="39"/>
       <c r="D48" s="39"/>
@@ -6687,10 +6704,10 @@
     </row>
     <row r="49" spans="1:59" ht="13.5" customHeight="1">
       <c r="A49" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="B49" s="41" t="s">
         <v>123</v>
-      </c>
-      <c r="B49" s="41" t="s">
-        <v>124</v>
       </c>
       <c r="C49" s="39"/>
       <c r="D49" s="39"/>
@@ -6752,10 +6769,10 @@
     </row>
     <row r="50" spans="1:59" ht="13.5" customHeight="1">
       <c r="A50" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="B50" s="38" t="s">
         <v>125</v>
-      </c>
-      <c r="B50" s="38" t="s">
-        <v>126</v>
       </c>
       <c r="C50" s="39"/>
       <c r="D50" s="39"/>
@@ -6817,10 +6834,10 @@
     </row>
     <row r="51" spans="1:59" ht="13.5" customHeight="1">
       <c r="A51" s="60" t="s">
+        <v>126</v>
+      </c>
+      <c r="B51" s="61" t="s">
         <v>127</v>
-      </c>
-      <c r="B51" s="61" t="s">
-        <v>128</v>
       </c>
       <c r="C51" s="36"/>
       <c r="D51" s="36"/>
@@ -6882,10 +6899,10 @@
     </row>
     <row r="52" spans="1:59" ht="13.5" customHeight="1">
       <c r="A52" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="B52" s="38" t="s">
         <v>129</v>
-      </c>
-      <c r="B52" s="38" t="s">
-        <v>130</v>
       </c>
       <c r="C52" s="39"/>
       <c r="D52" s="39"/>
@@ -6949,7 +6966,7 @@
     <row r="54" spans="1:59" ht="15.75" customHeight="1"/>
     <row r="55" spans="1:59" ht="15.75" customHeight="1">
       <c r="A55" s="25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B55" s="63"/>
       <c r="C55" s="64"/>
@@ -6962,28 +6979,28 @@
     </row>
     <row r="56" spans="1:59" ht="15.75" customHeight="1">
       <c r="B56" s="71" t="s">
+        <v>145</v>
+      </c>
+      <c r="C56" s="71" t="s">
         <v>146</v>
       </c>
-      <c r="C56" s="71" t="s">
+      <c r="D56" s="71" t="s">
         <v>147</v>
       </c>
-      <c r="D56" s="71" t="s">
+      <c r="E56" s="71" t="s">
         <v>148</v>
       </c>
-      <c r="E56" s="71" t="s">
+      <c r="F56" s="71" t="s">
         <v>149</v>
       </c>
-      <c r="F56" s="71" t="s">
+      <c r="G56" s="71" t="s">
         <v>150</v>
       </c>
-      <c r="G56" s="71" t="s">
+      <c r="H56" s="71" t="s">
         <v>151</v>
       </c>
-      <c r="H56" s="71" t="s">
+      <c r="I56" s="71" t="s">
         <v>152</v>
-      </c>
-      <c r="I56" s="71" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="57" spans="1:59" ht="15.75" customHeight="1"/>
